--- a/Output/Output Report.xlsx
+++ b/Output/Output Report.xlsx
@@ -1,107 +1,108 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <bookViews>
-    <workbookView xWindow="204" yWindow="588" windowWidth="22716" windowHeight="8676"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="124519"/>
-</workbook>
+<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <x:workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <x:bookViews>
+    <x:workbookView xWindow="204" yWindow="588" windowWidth="22716" windowHeight="8676" firstSheet="0" activeTab="0"/>
+  </x:bookViews>
+  <x:sheets>
+    <x:sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <x:sheet name="Sheet2" sheetId="2" r:id="rId5"/>
+  </x:sheets>
+  <x:definedNames/>
+  <x:calcPr calcId="124519"/>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
-  <si>
-    <t>ServerName</t>
-  </si>
-  <si>
-    <t>ServerName - Confidence</t>
-  </si>
-  <si>
-    <t>ServerName - OCR Confidence</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Total - Confidence</t>
-  </si>
-  <si>
-    <t>Total - OCR Confidence</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Date - Confidence</t>
-  </si>
-  <si>
-    <t>Date - OCR Confidence</t>
-  </si>
-  <si>
-    <t>misheel</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>0.98999995</t>
-  </si>
-  <si>
-    <t>19.88</t>
-  </si>
-  <si>
-    <t>04/13/2019</t>
-  </si>
-  <si>
-    <t>0.85999995</t>
-  </si>
-</sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:si>
+    <x:t>AccountNumber</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AccountNumber - Confidence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AccountNumber - OCR Confidence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>InvoiceNumber</x:t>
+  </x:si>
+  <x:si>
+    <x:t>InvoiceNumber - Confidence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>InvoiceNumber - OCR Confidence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Date</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Date - Confidence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Date - OCR Confidence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4554352</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.98999995</x:t>
+  </x:si>
+  <x:si>
+    <x:t>143453775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01-03-2019</x:t>
+  </x:si>
+</x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-</styleSheet>
+<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="0" formatCode=""/>
+  </x:numFmts>
+  <x:fonts count="1">
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+  </x:fonts>
+  <x:fills count="2">
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+  </x:fills>
+  <x:borders count="1">
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+  </x:borders>
+  <x:cellStyleXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
+  </x:cellStyleXfs>
+  <x:cellXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+  </x:cellXfs>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </x:cellStyles>
+  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+</x:styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -388,80 +389,126 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.88671875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:I2"/>
+  <x:sheetFormatPr defaultRowHeight="14.4"/>
+  <x:cols>
+    <x:col min="1" max="1" width="11" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="22.109375" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="3" max="3" width="26.21875" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="4" max="4" width="5.554688" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="5" max="5" width="16.109375" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="6" max="6" width="20.21875" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="7" max="7" width="10.554688" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="8" max="8" width="15.777344" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="9" max="9" width="19.886719" style="0" bestFit="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:9">
+      <x:c r="A1" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D1" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E1" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F1" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G1" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H1" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I1" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:9">
+      <x:c r="A2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:C2"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1" spans="1:3">
+      <x:c r="A1" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C1" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:3">
+      <x:c r="A2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>